--- a/PROJECT-CTD-FINANCING-WS.xlsx
+++ b/PROJECT-CTD-FINANCING-WS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikolas\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58297AE0-58AF-4C0E-A943-9371E06ABB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E437DC0-3EF6-465A-A1BD-90162A513E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3DCF5A8D-45A8-43FD-93EA-9C8C9B9C0CC5}"/>
   </bookViews>
@@ -322,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -330,9 +330,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -746,46 +745,46 @@
       <c r="N4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="S4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="U4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="V4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="W4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="X4" s="8" t="s">
+      <c r="X4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="Y4" s="9" t="s">
+      <c r="Y4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="AA4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AB4" s="8" t="s">
+      <c r="AB4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="AC4" s="8" t="s">
+      <c r="AC4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AD4" s="7" t="s">
+      <c r="AD4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AE4" s="9" t="s">
+      <c r="AE4" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -859,12 +858,12 @@
         <v>99.562314358974348</v>
       </c>
       <c r="X5" s="4">
-        <f>P5-V5</f>
-        <v>-0.39363304029303947</v>
-      </c>
-      <c r="Y5" s="10">
-        <f>P5-W5</f>
-        <v>-1.3057209523809519</v>
+        <f>V5-P5</f>
+        <v>0.39363304029303947</v>
+      </c>
+      <c r="Y5" s="9">
+        <f>W5-P5</f>
+        <v>1.3057209523809519</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4">
@@ -880,12 +879,12 @@
         <v>90.841087912087914</v>
       </c>
       <c r="AD5" s="4">
-        <f>P5-AB5</f>
-        <v>8.3275934065933939</v>
-      </c>
-      <c r="AE5" s="10">
-        <f>P5-AC5</f>
-        <v>7.4155054945054815</v>
+        <f>AB5-P5</f>
+        <v>-8.3275934065933939</v>
+      </c>
+      <c r="AE5" s="9">
+        <f>AC5-P5</f>
+        <v>-7.4155054945054815</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -958,12 +957,12 @@
         <v>100.34735002747253</v>
       </c>
       <c r="X6" s="5">
-        <f>P6-V6</f>
-        <v>-5.2844532967029068E-2</v>
-      </c>
-      <c r="Y6" s="11">
-        <f>P6-W6</f>
-        <v>-1.2410313461538465</v>
+        <f>V6-P6</f>
+        <v>5.2844532967029068E-2</v>
+      </c>
+      <c r="Y6" s="10">
+        <f>W6-P6</f>
+        <v>1.2410313461538465</v>
       </c>
       <c r="Z6" s="5"/>
       <c r="AA6" s="5">
@@ -979,12 +978,12 @@
         <v>94.384311813186827</v>
       </c>
       <c r="AD6" s="5">
-        <f>P6-AB6</f>
-        <v>5.910193681318674</v>
-      </c>
-      <c r="AE6" s="11">
-        <f>P6-AC6</f>
-        <v>4.7220068681318565</v>
+        <f>AB6-P6</f>
+        <v>-5.910193681318674</v>
+      </c>
+      <c r="AE6" s="10">
+        <f>AC6-P6</f>
+        <v>-4.7220068681318565</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1057,12 +1056,12 @@
         <v>100.06475010683761</v>
       </c>
       <c r="X7" s="4">
-        <f t="shared" ref="X7:X29" si="8">P7-V7</f>
-        <v>0.83195318986568623</v>
-      </c>
-      <c r="Y7" s="10">
-        <f t="shared" ref="Y7:Y29" si="9">P7-W7</f>
-        <v>-0.44551933760683937</v>
+        <f t="shared" ref="X7:X29" si="8">V7-P7</f>
+        <v>-0.83195318986568623</v>
+      </c>
+      <c r="Y7" s="9">
+        <f t="shared" ref="Y7:Y29" si="9">W7-P7</f>
+        <v>0.44551933760683937</v>
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4">
@@ -1078,12 +1077,12 @@
         <v>97.408472527472526</v>
       </c>
       <c r="AD7" s="4">
-        <f t="shared" ref="AD7:AD29" si="12">P7-AB7</f>
-        <v>3.4882307692307677</v>
-      </c>
-      <c r="AE7" s="10">
-        <f t="shared" ref="AE7:AE29" si="13">P7-AC7</f>
-        <v>2.2107582417582421</v>
+        <f t="shared" ref="AD7:AD29" si="12">AB7-P7</f>
+        <v>-3.4882307692307677</v>
+      </c>
+      <c r="AE7" s="9">
+        <f t="shared" ref="AE7:AE29" si="13">AC7-P7</f>
+        <v>-2.2107582417582421</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1157,11 +1156,11 @@
       </c>
       <c r="X8" s="5">
         <f t="shared" si="8"/>
-        <v>0.55535679487179834</v>
-      </c>
-      <c r="Y8" s="11">
+        <v>-0.55535679487179834</v>
+      </c>
+      <c r="Y8" s="10">
         <f t="shared" si="9"/>
-        <v>-1.1850278205128149</v>
+        <v>1.1850278205128149</v>
       </c>
       <c r="Z8" s="5"/>
       <c r="AA8" s="5">
@@ -1178,11 +1177,11 @@
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="12"/>
-        <v>1.463019230769234</v>
-      </c>
-      <c r="AE8" s="11">
+        <v>-1.463019230769234</v>
+      </c>
+      <c r="AE8" s="10">
         <f t="shared" si="13"/>
-        <v>-0.27736538461537918</v>
+        <v>0.27736538461537918</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1256,11 +1255,11 @@
       </c>
       <c r="X9" s="4">
         <f t="shared" si="8"/>
-        <v>0.64843343101343009</v>
-      </c>
-      <c r="Y9" s="10">
+        <v>-0.64843343101343009</v>
+      </c>
+      <c r="Y9" s="9">
         <f t="shared" si="9"/>
-        <v>-1.1427753601953583</v>
+        <v>1.1427753601953583</v>
       </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4">
@@ -1277,11 +1276,11 @@
       </c>
       <c r="AD9" s="4">
         <f t="shared" si="12"/>
-        <v>-0.70278021978022309</v>
-      </c>
-      <c r="AE9" s="10">
+        <v>0.70278021978022309</v>
+      </c>
+      <c r="AE9" s="9">
         <f t="shared" si="13"/>
-        <v>-2.4939890109890115</v>
+        <v>2.4939890109890115</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1355,11 +1354,11 @@
       </c>
       <c r="X10" s="5">
         <f t="shared" si="8"/>
-        <v>1.1923101266788763</v>
-      </c>
-      <c r="Y10" s="11">
+        <v>-1.1923101266788763</v>
+      </c>
+      <c r="Y10" s="10">
         <f t="shared" si="9"/>
-        <v>-1.1195030601343063</v>
+        <v>1.1195030601343063</v>
       </c>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5">
@@ -1376,11 +1375,11 @@
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="12"/>
-        <v>-2.6917994505494391</v>
-      </c>
-      <c r="AE10" s="11">
+        <v>2.6917994505494391</v>
+      </c>
+      <c r="AE10" s="10">
         <f t="shared" si="13"/>
-        <v>-5.0036126373626217</v>
+        <v>5.0036126373626217</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1454,11 +1453,11 @@
       </c>
       <c r="X11" s="4">
         <f t="shared" si="8"/>
-        <v>1.0941640354090225</v>
-      </c>
-      <c r="Y11" s="10">
+        <v>-1.0941640354090225</v>
+      </c>
+      <c r="Y11" s="9">
         <f t="shared" si="9"/>
-        <v>-1.0899018986569047</v>
+        <v>1.0899018986569047</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4">
@@ -1475,11 +1474,11 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" si="12"/>
-        <v>-5.5114203296703437</v>
-      </c>
-      <c r="AE11" s="10">
+        <v>5.5114203296703437</v>
+      </c>
+      <c r="AE11" s="9">
         <f t="shared" si="13"/>
-        <v>-7.6954862637362851</v>
+        <v>7.6954862637362851</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1535,7 +1534,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y12" s="11" t="e">
+      <c r="Y12" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -1556,7 +1555,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE12" s="11" t="e">
+      <c r="AE12" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -1614,7 +1613,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y13" s="10" t="e">
+      <c r="Y13" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -1635,7 +1634,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE13" s="10" t="e">
+      <c r="AE13" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -1693,7 +1692,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y14" s="11" t="e">
+      <c r="Y14" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -1714,7 +1713,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE14" s="11" t="e">
+      <c r="AE14" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -1772,7 +1771,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y15" s="10" t="e">
+      <c r="Y15" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -1793,7 +1792,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE15" s="10" t="e">
+      <c r="AE15" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -1851,7 +1850,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y16" s="11" t="e">
+      <c r="Y16" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -1872,7 +1871,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE16" s="11" t="e">
+      <c r="AE16" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -1930,7 +1929,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y17" s="10" t="e">
+      <c r="Y17" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -1951,7 +1950,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE17" s="10" t="e">
+      <c r="AE17" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2009,7 +2008,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y18" s="11" t="e">
+      <c r="Y18" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2030,7 +2029,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE18" s="11" t="e">
+      <c r="AE18" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2088,7 +2087,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y19" s="10" t="e">
+      <c r="Y19" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2109,7 +2108,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE19" s="10" t="e">
+      <c r="AE19" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2167,7 +2166,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y20" s="11" t="e">
+      <c r="Y20" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2188,7 +2187,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE20" s="11" t="e">
+      <c r="AE20" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2246,7 +2245,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y21" s="10" t="e">
+      <c r="Y21" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2267,7 +2266,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE21" s="10" t="e">
+      <c r="AE21" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2325,7 +2324,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y22" s="11" t="e">
+      <c r="Y22" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2346,7 +2345,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE22" s="11" t="e">
+      <c r="AE22" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2404,7 +2403,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y23" s="10" t="e">
+      <c r="Y23" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2425,7 +2424,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE23" s="10" t="e">
+      <c r="AE23" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2483,7 +2482,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y24" s="11" t="e">
+      <c r="Y24" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2504,7 +2503,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE24" s="11" t="e">
+      <c r="AE24" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2562,7 +2561,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y25" s="10" t="e">
+      <c r="Y25" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2583,7 +2582,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE25" s="10" t="e">
+      <c r="AE25" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2641,7 +2640,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y26" s="11" t="e">
+      <c r="Y26" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2662,7 +2661,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE26" s="11" t="e">
+      <c r="AE26" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2720,7 +2719,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y27" s="10" t="e">
+      <c r="Y27" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2741,7 +2740,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE27" s="10" t="e">
+      <c r="AE27" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2799,7 +2798,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y28" s="11" t="e">
+      <c r="Y28" s="10" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2820,7 +2819,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE28" s="11" t="e">
+      <c r="AE28" s="10" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2878,7 +2877,7 @@
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y29" s="10" t="e">
+      <c r="Y29" s="9" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -2899,7 +2898,7 @@
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE29" s="10" t="e">
+      <c r="AE29" s="9" t="e">
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
@@ -2909,10 +2908,10 @@
       <c r="B31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="2:31" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
@@ -2937,15 +2936,15 @@
       </c>
       <c r="G33" s="4">
         <f>_xlfn.AGGREGATE(15,6,AE5:AE29,1)</f>
-        <v>-7.6954862637362851</v>
+        <v>-7.4155054945054815</v>
       </c>
       <c r="H33" s="4">
         <f>_xlfn.AGGREGATE(15,6,Y5:Y29,1)</f>
-        <v>-1.3057209523809519</v>
+        <v>0.44551933760683937</v>
       </c>
       <c r="I33" s="4">
         <f>G33-H33</f>
-        <v>-6.3897653113553332</v>
+        <v>-7.8610248321123208</v>
       </c>
       <c r="J33" s="4" t="str">
         <f>IF(I33&gt;0,"Rich",IF(I33&lt;0,"Cheap","Fair"))</f>
@@ -3103,18 +3102,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3136,14 +3135,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C30215E4-F248-40B5-A60E-BF7E871E0D99}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29D6F9B8-231C-43AC-8581-7797907C3C11}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -3157,4 +3148,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C30215E4-F248-40B5-A60E-BF7E871E0D99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/PROJECT-CTD-FINANCING-WS.xlsx
+++ b/PROJECT-CTD-FINANCING-WS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikolas\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E437DC0-3EF6-465A-A1BD-90162A513E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60B9668-247D-4EFC-B66B-B9266A4075D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3DCF5A8D-45A8-43FD-93EA-9C8C9B9C0CC5}"/>
   </bookViews>
@@ -858,12 +858,12 @@
         <v>99.562314358974348</v>
       </c>
       <c r="X5" s="4">
-        <f>V5-P5</f>
-        <v>0.39363304029303947</v>
+        <f>P5-V5</f>
+        <v>-0.39363304029303947</v>
       </c>
       <c r="Y5" s="9">
-        <f>W5-P5</f>
-        <v>1.3057209523809519</v>
+        <f>P5-W5</f>
+        <v>-1.3057209523809519</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4">
@@ -879,12 +879,12 @@
         <v>90.841087912087914</v>
       </c>
       <c r="AD5" s="4">
-        <f>AB5-P5</f>
-        <v>-8.3275934065933939</v>
+        <f>P5-AB5</f>
+        <v>8.3275934065933939</v>
       </c>
       <c r="AE5" s="9">
-        <f>AC5-P5</f>
-        <v>-7.4155054945054815</v>
+        <f>P5-AC5</f>
+        <v>7.4155054945054815</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -957,12 +957,12 @@
         <v>100.34735002747253</v>
       </c>
       <c r="X6" s="5">
-        <f>V6-P6</f>
-        <v>5.2844532967029068E-2</v>
+        <f>P6-V6</f>
+        <v>-5.2844532967029068E-2</v>
       </c>
       <c r="Y6" s="10">
-        <f>W6-P6</f>
-        <v>1.2410313461538465</v>
+        <f>P6-W6</f>
+        <v>-1.2410313461538465</v>
       </c>
       <c r="Z6" s="5"/>
       <c r="AA6" s="5">
@@ -978,12 +978,12 @@
         <v>94.384311813186827</v>
       </c>
       <c r="AD6" s="5">
-        <f>AB6-P6</f>
-        <v>-5.910193681318674</v>
+        <f>P6-AB6</f>
+        <v>5.910193681318674</v>
       </c>
       <c r="AE6" s="10">
-        <f>AC6-P6</f>
-        <v>-4.7220068681318565</v>
+        <f>P6-AC6</f>
+        <v>4.7220068681318565</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1056,12 +1056,12 @@
         <v>100.06475010683761</v>
       </c>
       <c r="X7" s="4">
-        <f t="shared" ref="X7:X29" si="8">V7-P7</f>
-        <v>-0.83195318986568623</v>
+        <f t="shared" ref="X7:X29" si="8">P7-V7</f>
+        <v>0.83195318986568623</v>
       </c>
       <c r="Y7" s="9">
-        <f t="shared" ref="Y7:Y29" si="9">W7-P7</f>
-        <v>0.44551933760683937</v>
+        <f t="shared" ref="Y7:Y29" si="9">P7-W7</f>
+        <v>-0.44551933760683937</v>
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4">
@@ -1077,12 +1077,12 @@
         <v>97.408472527472526</v>
       </c>
       <c r="AD7" s="4">
-        <f t="shared" ref="AD7:AD29" si="12">AB7-P7</f>
-        <v>-3.4882307692307677</v>
+        <f t="shared" ref="AD7:AD29" si="12">P7-AB7</f>
+        <v>3.4882307692307677</v>
       </c>
       <c r="AE7" s="9">
-        <f t="shared" ref="AE7:AE29" si="13">AC7-P7</f>
-        <v>-2.2107582417582421</v>
+        <f t="shared" ref="AE7:AE29" si="13">P7-AC7</f>
+        <v>2.2107582417582421</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1156,11 +1156,11 @@
       </c>
       <c r="X8" s="5">
         <f t="shared" si="8"/>
-        <v>-0.55535679487179834</v>
+        <v>0.55535679487179834</v>
       </c>
       <c r="Y8" s="10">
         <f t="shared" si="9"/>
-        <v>1.1850278205128149</v>
+        <v>-1.1850278205128149</v>
       </c>
       <c r="Z8" s="5"/>
       <c r="AA8" s="5">
@@ -1177,11 +1177,11 @@
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="12"/>
-        <v>-1.463019230769234</v>
+        <v>1.463019230769234</v>
       </c>
       <c r="AE8" s="10">
         <f t="shared" si="13"/>
-        <v>0.27736538461537918</v>
+        <v>-0.27736538461537918</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1255,11 +1255,11 @@
       </c>
       <c r="X9" s="4">
         <f t="shared" si="8"/>
-        <v>-0.64843343101343009</v>
+        <v>0.64843343101343009</v>
       </c>
       <c r="Y9" s="9">
         <f t="shared" si="9"/>
-        <v>1.1427753601953583</v>
+        <v>-1.1427753601953583</v>
       </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4">
@@ -1276,11 +1276,11 @@
       </c>
       <c r="AD9" s="4">
         <f t="shared" si="12"/>
-        <v>0.70278021978022309</v>
+        <v>-0.70278021978022309</v>
       </c>
       <c r="AE9" s="9">
         <f t="shared" si="13"/>
-        <v>2.4939890109890115</v>
+        <v>-2.4939890109890115</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1354,11 +1354,11 @@
       </c>
       <c r="X10" s="5">
         <f t="shared" si="8"/>
-        <v>-1.1923101266788763</v>
+        <v>1.1923101266788763</v>
       </c>
       <c r="Y10" s="10">
         <f t="shared" si="9"/>
-        <v>1.1195030601343063</v>
+        <v>-1.1195030601343063</v>
       </c>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5">
@@ -1375,11 +1375,11 @@
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="12"/>
-        <v>2.6917994505494391</v>
+        <v>-2.6917994505494391</v>
       </c>
       <c r="AE10" s="10">
         <f t="shared" si="13"/>
-        <v>5.0036126373626217</v>
+        <v>-5.0036126373626217</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1453,11 +1453,11 @@
       </c>
       <c r="X11" s="4">
         <f t="shared" si="8"/>
-        <v>-1.0941640354090225</v>
+        <v>1.0941640354090225</v>
       </c>
       <c r="Y11" s="9">
         <f t="shared" si="9"/>
-        <v>1.0899018986569047</v>
+        <v>-1.0899018986569047</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4">
@@ -1474,11 +1474,11 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" si="12"/>
-        <v>5.5114203296703437</v>
+        <v>-5.5114203296703437</v>
       </c>
       <c r="AE11" s="9">
         <f t="shared" si="13"/>
-        <v>7.6954862637362851</v>
+        <v>-7.6954862637362851</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2936,15 +2936,15 @@
       </c>
       <c r="G33" s="4">
         <f>_xlfn.AGGREGATE(15,6,AE5:AE29,1)</f>
-        <v>-7.4155054945054815</v>
+        <v>-7.6954862637362851</v>
       </c>
       <c r="H33" s="4">
         <f>_xlfn.AGGREGATE(15,6,Y5:Y29,1)</f>
-        <v>0.44551933760683937</v>
+        <v>-1.3057209523809519</v>
       </c>
       <c r="I33" s="4">
         <f>G33-H33</f>
-        <v>-7.8610248321123208</v>
+        <v>-6.3897653113553332</v>
       </c>
       <c r="J33" s="4" t="str">
         <f>IF(I33&gt;0,"Rich",IF(I33&lt;0,"Cheap","Fair"))</f>
